--- a/demo/samples/practice/03-outstanding.xlsx
+++ b/demo/samples/practice/03-outstanding.xlsx
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
       <c r="E6" t="n">
         <v>84600</v>
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E7" t="n">
         <v>47250</v>
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="E8" t="n">
         <v>19800</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="E9" t="n">
         <v>31450</v>
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="E10" t="n">
         <v>12900</v>
